--- a/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K58.xlsx
+++ b/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K58.xlsx
@@ -177,7 +177,7 @@
     <t>Đây là số tối thiểu đã biết, không phải sĩ số đầu khoá. Cần thay bằng sĩ số đầu khoá chính thức nếu có.</t>
   </si>
   <si>
-    <t>Các dòng có nhiều tên ngành mâu thuẫn không được đưa vào sheet import và nằm trong sheet “Đối chiếu nguồn”.</t>
+    <t>Các mã lớp có tên ngành nguồn mâu thuẫn vẫn được đưa vào import theo quy tắc mã lớp; chi tiết nằm trong sheet “Đối chiếu nguồn”.</t>
   </si>
 </sst>
 </file>

--- a/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K58.xlsx
+++ b/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K58.xlsx
@@ -6,14 +6,15 @@
   <sheets>
     <sheet sheetId="1" name="Khoa nganh dao tao" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Đối chiếu nguồn" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Hướng dẫn" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Nguồn chỉ tiêu" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Hướng dẫn" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="95">
   <si>
     <t>Khoá ngành đào tạo</t>
   </si>
@@ -21,7 +22,7 @@
     <t>Ngành đào tạo</t>
   </si>
   <si>
-    <t>Số lượng sinh viên</t>
+    <t>Số lượng sinh viên đầu vào</t>
   </si>
   <si>
     <t>BMM58ĐH</t>
@@ -156,35 +157,155 @@
     <t>Kết luận</t>
   </si>
   <si>
+    <t>Mã CTĐT tuyển sinh</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu công bố</t>
+  </si>
+  <si>
+    <t>Số đầu vào tạm tính áp dụng</t>
+  </si>
+  <si>
+    <t>Căn cứ áp dụng</t>
+  </si>
+  <si>
     <t>K58</t>
   </si>
   <si>
     <t>Đủ điều kiện import</t>
   </si>
   <si>
+    <t>A403</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu tuyển sinh công bố</t>
+  </si>
+  <si>
+    <t>D117</t>
+  </si>
+  <si>
+    <t>D101</t>
+  </si>
+  <si>
+    <t>H105</t>
+  </si>
+  <si>
+    <t>D105</t>
+  </si>
+  <si>
+    <t>D104</t>
+  </si>
+  <si>
+    <t>A408</t>
+  </si>
+  <si>
+    <t>A409</t>
+  </si>
+  <si>
+    <t>D118</t>
+  </si>
+  <si>
+    <t>H401</t>
+  </si>
+  <si>
+    <t>D401</t>
+  </si>
+  <si>
+    <t>D127</t>
+  </si>
+  <si>
+    <t>H402</t>
+  </si>
+  <si>
+    <t>D402</t>
+  </si>
+  <si>
+    <t>D407</t>
+  </si>
+  <si>
+    <t>D403</t>
+  </si>
+  <si>
+    <t>D121</t>
+  </si>
+  <si>
+    <t>D119</t>
+  </si>
+  <si>
+    <t>D112</t>
+  </si>
+  <si>
+    <t>THÔNG TIN NGUỒN</t>
+  </si>
+  <si>
+    <t>GIÁ TRỊ</t>
+  </si>
+  <si>
+    <t>Khóa</t>
+  </si>
+  <si>
+    <t>Năm tuyển sinh</t>
+  </si>
+  <si>
+    <t>Loại dữ liệu</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu tuyển sinh dùng làm số đầu vào tạm tính; KHÔNG phải số sinh viên thực nhập</t>
+  </si>
+  <si>
+    <t>Loại nguồn</t>
+  </si>
+  <si>
+    <t>official_admission_announcement</t>
+  </si>
+  <si>
+    <t>Nguồn</t>
+  </si>
+  <si>
+    <t>https://tuyensinh.vimaru.edu.vn/node/236</t>
+  </si>
+  <si>
+    <t>Nguyên tắc</t>
+  </si>
+  <si>
+    <t>Số áp dụng = max(chỉ tiêu công bố, số sinh viên tốt nghiệp duy nhất đã quan sát) để không tạo tỷ lệ tốt nghiệp vượt 100%</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Thay bằng số thực nhập chính thức khi Nhà trường cung cấp dữ liệu.</t>
+  </si>
+  <si>
     <t>HƯỚNG DẪN</t>
   </si>
   <si>
-    <t>Khi import, chọn đúng K58 ở trường “Import vào khoá học”.</t>
+    <t>Khi import, chọn đúng K58 ở trường “Import vào khóa học”.</t>
+  </si>
+  <si>
+    <t>File này chỉ được chứa mã lớp của K58; hệ thống sẽ từ chối file chứa từ hai khóa trở lên.</t>
   </si>
   <si>
     <t>Sheet “Khoa nganh dao tao” là dữ liệu import; hệ thống chỉ đọc sheet đầu tiên.</t>
   </si>
   <si>
-    <t>Số lượng sinh viên trong file này là số mã sinh viên duy nhất quan sát được trong các file tốt nghiệp nguồn.</t>
-  </si>
-  <si>
-    <t>Đây là số tối thiểu đã biết, không phải sĩ số đầu khoá. Cần thay bằng sĩ số đầu khoá chính thức nếu có.</t>
-  </si>
-  <si>
-    <t>Các mã lớp có tên ngành nguồn mâu thuẫn vẫn được đưa vào import theo quy tắc mã lớp; chi tiết nằm trong sheet “Đối chiếu nguồn”.</t>
+    <t>Cột số lượng sinh viên đầu vào hiện dùng chỉ tiêu tuyển sinh công bố làm dữ liệu tạm tính, không phải số thực nhập.</t>
+  </si>
+  <si>
+    <t>Nếu số tốt nghiệp quan sát được lớn hơn chỉ tiêu, file dùng số tốt nghiệp làm cận dưới để tránh tỷ lệ vượt 100%.</t>
+  </si>
+  <si>
+    <t>Xem nguồn, năm công bố và nguyên tắc áp dụng tại sheet “Nguồn chỉ tiêu”.</t>
+  </si>
+  <si>
+    <t>Cần thay dữ liệu tạm tính bằng số thực nhập khi Nhà trường cung cấp dữ liệu chính thức.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -195,9 +316,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
     </font>
     <font>
       <b/>
@@ -229,13 +347,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,10 +706,10 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -602,7 +728,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -613,7 +739,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -624,7 +750,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -635,7 +761,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -646,7 +772,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -657,7 +783,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -668,7 +794,7 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -679,7 +805,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>21</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -690,7 +816,7 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -701,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -712,7 +838,7 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -723,7 +849,7 @@
         <v>26</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -734,7 +860,7 @@
         <v>28</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -745,7 +871,7 @@
         <v>30</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -756,7 +882,7 @@
         <v>32</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -767,7 +893,7 @@
         <v>34</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -778,7 +904,7 @@
         <v>36</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -789,7 +915,7 @@
         <v>38</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -800,19 +926,19 @@
         <v>40</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -821,31 +947,46 @@
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="70" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -860,12 +1001,24 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2">
+        <v>45</v>
+      </c>
+      <c r="I2">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -880,12 +1033,24 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -900,12 +1065,24 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
+        <v>180</v>
+      </c>
+      <c r="I4">
+        <v>180</v>
+      </c>
+      <c r="J4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -920,12 +1097,24 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5">
+        <v>45</v>
+      </c>
+      <c r="I5">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -940,12 +1129,24 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6">
+        <v>90</v>
+      </c>
+      <c r="I6">
+        <v>90</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -960,12 +1161,24 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7">
+        <v>90</v>
+      </c>
+      <c r="I7">
+        <v>90</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -980,12 +1193,24 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -1000,12 +1225,24 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>80</v>
+      </c>
+      <c r="I9">
+        <v>80</v>
+      </c>
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -1020,12 +1257,24 @@
         <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10">
+        <v>45</v>
+      </c>
+      <c r="I10">
+        <v>45</v>
+      </c>
+      <c r="J10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -1040,12 +1289,24 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11">
+        <v>90</v>
+      </c>
+      <c r="I11">
+        <v>90</v>
+      </c>
+      <c r="J11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
@@ -1060,12 +1321,24 @@
         <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12">
+        <v>135</v>
+      </c>
+      <c r="I12">
+        <v>135</v>
+      </c>
+      <c r="J12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
@@ -1080,12 +1353,24 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13">
+        <v>45</v>
+      </c>
+      <c r="I13">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -1100,12 +1385,24 @@
         <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14">
+        <v>90</v>
+      </c>
+      <c r="I14">
+        <v>90</v>
+      </c>
+      <c r="J14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
@@ -1120,12 +1417,24 @@
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15">
+        <v>135</v>
+      </c>
+      <c r="I15">
+        <v>135</v>
+      </c>
+      <c r="J15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -1140,12 +1449,24 @@
         <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16">
+        <v>135</v>
+      </c>
+      <c r="I16">
+        <v>135</v>
+      </c>
+      <c r="J16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -1160,12 +1481,24 @@
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17">
+        <v>90</v>
+      </c>
+      <c r="I17">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
@@ -1180,12 +1513,24 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18">
+        <v>90</v>
+      </c>
+      <c r="I18">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -1200,12 +1545,24 @@
         <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19">
+        <v>45</v>
+      </c>
+      <c r="I19">
+        <v>45</v>
+      </c>
+      <c r="J19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
@@ -1220,52 +1577,153 @@
         <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="G20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20">
+        <v>90</v>
+      </c>
+      <c r="I20">
+        <v>90</v>
+      </c>
+      <c r="J20" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="115" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="100" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>81</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
